--- a/data/trans_orig/IP13-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP13-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>45176</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>51088</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54672</t>
+          <t>55281</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59541</t>
+          <t>60217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102120</t>
+          <t>102316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110012</t>
+          <t>110154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19313</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90854</t>
+          <t>90855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98440</t>
+          <t>98353</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96418</t>
+          <t>96954</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105003</t>
+          <t>104921</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191006</t>
+          <t>190239</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>202072</t>
+          <t>201883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62833</t>
+          <t>62335</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66041</t>
+          <t>66038</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131032</t>
+          <t>131267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>15704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67891</t>
+          <t>67487</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73708</t>
+          <t>73695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67404</t>
+          <t>67710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75927</t>
+          <t>75857</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138788</t>
+          <t>138268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>148512</t>
+          <t>148477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37705</t>
+          <t>37203</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41473</t>
+          <t>41474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81251</t>
+          <t>81736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86070</t>
+          <t>86076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>884</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51028</t>
+          <t>50746</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54754</t>
+          <t>55797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>108288</t>
+          <t>108504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115116</t>
+          <t>114903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116268</t>
+          <t>117583</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>125234</t>
+          <t>125298</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127569</t>
+          <t>128178</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248364</t>
+          <t>249300</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>258956</t>
+          <t>259407</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>21383</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14647</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27562</t>
+          <t>28229</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>146453</t>
+          <t>146464</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154712</t>
+          <t>154280</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>144129</t>
+          <t>142675</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>154701</t>
+          <t>155060</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>294400</t>
+          <t>293733</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>307315</t>
+          <t>307134</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23151</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39863</t>
+          <t>39327</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>27185</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44952</t>
+          <t>45549</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>54060</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>81258</t>
+          <t>80167</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>641158</t>
+          <t>641694</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>657870</t>
+          <t>658371</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>677748</t>
+          <t>677151</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>695220</t>
+          <t>695515</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1322463</t>
+          <t>1323554</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1349325</t>
+          <t>1349661</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2012 (tasa de respuesta: 99,71%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18883</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48007</t>
+          <t>48201</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55838</t>
+          <t>55819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>51101</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60791</t>
+          <t>60549</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103353</t>
+          <t>103053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114690</t>
+          <t>114536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>7848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19084</t>
+          <t>19322</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30354</t>
+          <t>30941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90036</t>
+          <t>89893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99356</t>
+          <t>99291</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92075</t>
+          <t>91837</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102937</t>
+          <t>103311</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185518</t>
+          <t>184931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200312</t>
+          <t>199461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10953</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17172</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58855</t>
+          <t>58774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66078</t>
+          <t>66069</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60647</t>
+          <t>60301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68541</t>
+          <t>68480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122260</t>
+          <t>121632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>133130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70927</t>
+          <t>71420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77125</t>
+          <t>77129</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72371</t>
+          <t>72135</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79585</t>
+          <t>79573</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146163</t>
+          <t>145570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155434</t>
+          <t>155137</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34813</t>
+          <t>34637</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42328</t>
+          <t>41788</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38939</t>
+          <t>38698</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45386</t>
+          <t>45379</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76287</t>
+          <t>76863</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86208</t>
+          <t>86364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>751</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51166</t>
+          <t>50971</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55385</t>
+          <t>55305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109544</t>
+          <t>108846</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115494</t>
+          <t>115479</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13471</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>129018</t>
+          <t>128989</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>136662</t>
+          <t>136675</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136753</t>
+          <t>136326</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143082</t>
+          <t>143447</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>269356</t>
+          <t>268951</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278850</t>
+          <t>278692</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20744</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>152404</t>
+          <t>152464</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160836</t>
+          <t>160868</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>158533</t>
+          <t>158619</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>167239</t>
+          <t>167464</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>314070</t>
+          <t>314276</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>326297</t>
+          <t>327000</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>29857</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49742</t>
+          <t>50555</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35851</t>
+          <t>36046</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57807</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71268</t>
+          <t>71740</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100565</t>
+          <t>101689</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>660440</t>
+          <t>659627</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>681251</t>
+          <t>680325</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>692626</t>
+          <t>692099</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>714582</t>
+          <t>714387</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1360050</t>
+          <t>1358926</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1389347</t>
+          <t>1388875</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>11602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52060</t>
+          <t>52533</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53373</t>
+          <t>52860</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61570</t>
+          <t>61707</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109008</t>
+          <t>107994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118235</t>
+          <t>118028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>17170</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11207</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>25644</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86296</t>
+          <t>86777</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96972</t>
+          <t>97277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99076</t>
+          <t>98263</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106964</t>
+          <t>106939</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>188674</t>
+          <t>188586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201946</t>
+          <t>201443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61985</t>
+          <t>62032</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66475</t>
+          <t>66469</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130737</t>
+          <t>130547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136077</t>
+          <t>136078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>11089</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15655</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69859</t>
+          <t>70232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76097</t>
+          <t>76158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70389</t>
+          <t>70095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78499</t>
+          <t>78438</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142490</t>
+          <t>143207</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153152</t>
+          <t>153286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35665</t>
+          <t>35766</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41717</t>
+          <t>42026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40712</t>
+          <t>41016</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45772</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78101</t>
+          <t>79290</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86502</t>
+          <t>86718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50607</t>
+          <t>50617</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52151</t>
+          <t>52830</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106682</t>
+          <t>106549</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11720</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>129457</t>
+          <t>129299</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>135853</t>
+          <t>136030</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>137822</t>
+          <t>137843</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143416</t>
+          <t>143409</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>269726</t>
+          <t>269476</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278354</t>
+          <t>278053</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16739</t>
+          <t>17597</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12636</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>13156</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>26174</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>147437</t>
+          <t>146579</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>157425</t>
+          <t>156908</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>158213</t>
+          <t>158008</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>167171</t>
+          <t>166921</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>308761</t>
+          <t>308851</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>322152</t>
+          <t>321869</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28467</t>
+          <t>28561</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47522</t>
+          <t>47171</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>24044</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44007</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>57121</t>
+          <t>57615</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>83544</t>
+          <t>83620</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>656849</t>
+          <t>657200</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>675904</t>
+          <t>675810</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>700837</t>
+          <t>701725</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>720231</t>
+          <t>720800</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1365671</t>
+          <t>1365595</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1392094</t>
+          <t>1391600</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66029</t>
+          <t>65515</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72490</t>
+          <t>72019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73354</t>
+          <t>73488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142573</t>
+          <t>142186</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150507</t>
+          <t>150724</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>11208</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>20405</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116244</t>
+          <t>115631</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125014</t>
+          <t>124974</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112611</t>
+          <t>112489</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>123154</t>
+          <t>122950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232031</t>
+          <t>234030</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>246290</t>
+          <t>246514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50007</t>
+          <t>49480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56855</t>
+          <t>56682</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58534</t>
+          <t>57920</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65890</t>
+          <t>65871</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111872</t>
+          <t>111299</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>121135</t>
+          <t>121174</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>10749</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63413</t>
+          <t>63636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69554</t>
+          <t>69559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69715</t>
+          <t>70534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137283</t>
+          <t>137529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>146795</t>
+          <t>146670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10873</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>28948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33598</t>
+          <t>33519</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32917</t>
+          <t>33470</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>39584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64925</t>
+          <t>64359</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72135</t>
+          <t>72062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38772</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44571</t>
+          <t>44523</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>48730</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54832</t>
+          <t>54919</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89908</t>
+          <t>90173</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98231</t>
+          <t>98568</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17773</t>
+          <t>17770</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10443</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>24795</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19295</t>
+          <t>19622</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37935</t>
+          <t>37419</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106735</t>
+          <t>106738</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117417</t>
+          <t>117881</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131092</t>
+          <t>130493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>144797</t>
+          <t>144845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>241862</t>
+          <t>242378</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>260502</t>
+          <t>260175</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15240</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20642</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122808</t>
+          <t>122743</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129471</t>
+          <t>129357</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>141555</t>
+          <t>141690</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152027</t>
+          <t>151952</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>267772</t>
+          <t>267406</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>279793</t>
+          <t>279841</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48293</t>
+          <t>47236</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36542</t>
+          <t>37418</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>59658</t>
+          <t>61482</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71310</t>
+          <t>71550</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>102119</t>
+          <t>102444</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>617047</t>
+          <t>618104</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>637527</t>
+          <t>637340</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>701590</t>
+          <t>699766</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>724706</t>
+          <t>723830</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1324469</t>
+          <t>1324144</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1355278</t>
+          <t>1355038</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
